--- a/Projet_2/Projet_2_31_mars.xlsx
+++ b/Projet_2/Projet_2_31_mars.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e8cc6f8fcd8ecae5/Bureau/Labos-TPOP/Projet_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{728F1329-7636-4B52-9E03-CB5B35F1ACDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02BBFEB2-C844-4FDA-BAB2-6F5A8C4C10D3}"/>
+  <xr:revisionPtr revIDLastSave="401" documentId="8_{728F1329-7636-4B52-9E03-CB5B35F1ACDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF63715-E078-4E78-82C0-641E823B73EA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B802390F-8502-4048-A121-AD453CA8ECAD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{B802390F-8502-4048-A121-AD453CA8ECAD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Essai1" sheetId="1" r:id="rId1"/>
+    <sheet name="Valeurs de base" sheetId="2" r:id="rId1"/>
+    <sheet name="Essai1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,25 +37,487 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="158">
+  <si>
+    <t>Angle polariseur 1</t>
+  </si>
+  <si>
+    <t>85 deg</t>
+  </si>
+  <si>
+    <t>5 deg par rapport à la vertical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modèle des polariseurs (socle): </t>
+  </si>
+  <si>
+    <t>Thorlabs PPM1</t>
+  </si>
+  <si>
+    <t>Polariseur (film):</t>
+  </si>
+  <si>
+    <t>Dichroïque</t>
+  </si>
+  <si>
+    <t>Longueur parcourure (cm)</t>
+  </si>
   <si>
     <t>Angle (deg) pol 2</t>
   </si>
   <si>
-    <t>Courant avec solution</t>
+    <t>Courant avec solution 45.45 g / 100ml a 25 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 45.45 g / 100ml a 19 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 45.45 g / 100ml a 15 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 45.45 g / 100ml a 11 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 45.45 g / 100ml a 7 ml</t>
   </si>
   <si>
     <t>Courant à vide</t>
   </si>
   <si>
-    <t>Longueur parcourure</t>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>18.8</t>
+  </si>
+  <si>
+    <t>20.7</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>24.9</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Concentration</t>
+  </si>
+  <si>
+    <t>17.1</t>
+  </si>
+  <si>
+    <t>21.5</t>
+  </si>
+  <si>
+    <t>23.3</t>
+  </si>
+  <si>
+    <t>25.8</t>
+  </si>
+  <si>
+    <t>25.2</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t>18.9</t>
+  </si>
+  <si>
+    <t>22.9</t>
+  </si>
+  <si>
+    <t>23.8</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>24.3</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>23.5</t>
+  </si>
+  <si>
+    <t>23.4</t>
+  </si>
+  <si>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>19.7</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>21.3</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>18.7</t>
+  </si>
+  <si>
+    <t>17.8</t>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>15.9</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>13.8</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>19.4</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>20.9</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
+    <t>10.9</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>25.7</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>23.1</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>21.7</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>21.6</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>17.6</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>14.0</t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>7.6</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>13.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>9.2</t>
+  </si>
+  <si>
+    <t>12.1</t>
+  </si>
+  <si>
+    <t>19.6</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>11.8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,7 +526,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -73,6 +536,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -89,9 +564,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,6 +588,2105 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Essai1!$I$2:$I$25</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>11.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10.3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Essai1!$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>456</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Essai1!I2:I27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-8657-477C-9FF1-3F8401E06040}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1269061640"/>
+        <c:axId val="522588168"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1269061640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522588168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="522588168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1269061640"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Essai1!$I$2:$I$25</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>11.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10.3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Essai1!$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>456</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Essai1!$I$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BF49-4FDE-A1E0-D4E6F958FC73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="200883719"/>
+        <c:axId val="200914951"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="200883719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="200914951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="200914951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="200883719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1685925</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F7A3C24-FF8F-7EA1-F0FF-46BD99D9F0E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="381000"/>
+          <a:ext cx="1495425" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Graphique 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{701B826D-158E-0B28-3A28-599F9C531F65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Graphique 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEE62F1-D558-B19C-313C-62985EAB74DF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{701B826D-158E-0B28-3A28-599F9C531F65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,31 +3005,1146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474AC0C1-7935-42B0-AFD9-FC74ED331F55}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4C76ED-C4D9-43CD-AE48-FF167CED520D}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474AC0C1-7935-42B0-AFD9-FC74ED331F55}">
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="2" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="43.5">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="B2">
+        <v>246</v>
+      </c>
+      <c r="C2">
+        <f>B2</f>
+        <v>246</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>256</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C13" si="0">B3</f>
+        <v>256</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4">
+        <v>266</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>266</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5">
+        <v>276</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>276</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6">
+        <v>286</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>286</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7">
+        <v>296</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>296</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8">
+        <v>306</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>306</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9">
+        <v>316</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>316</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10">
+        <v>326</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>326</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11">
+        <v>336</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>336</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12">
+        <v>346</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>346</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13">
+        <v>356</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>356</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <f>B14+360</f>
+        <v>366</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:C45" si="1">B15+360</f>
+        <v>376</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>386</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17">
+        <v>36</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>396</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>406</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19">
+        <v>56</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>416</v>
+      </c>
+      <c r="D19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20">
+        <v>66</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>426</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21">
+        <v>74</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22">
+        <v>76</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>436</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>105</v>
+      </c>
+      <c r="H22" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24">
+        <v>84</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25">
+        <v>86</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>446</v>
+      </c>
+      <c r="D25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27">
+        <v>96</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" t="s">
+        <v>113</v>
+      </c>
+      <c r="I27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29">
+        <v>101</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31">
+        <v>106</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>466</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32">
+        <v>111</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33">
+        <v>116</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>476</v>
+      </c>
+      <c r="D33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34">
+        <v>126</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>486</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35">
+        <v>136</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>496</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36">
+        <v>146</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>506</v>
+      </c>
+      <c r="D36" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="s">
+        <v>134</v>
+      </c>
+      <c r="G36" t="s">
+        <v>135</v>
+      </c>
+      <c r="H36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37">
+        <v>156</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>516</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38">
+        <v>166</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>526</v>
+      </c>
+      <c r="D38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38" t="s">
+        <v>79</v>
+      </c>
+      <c r="I38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39">
+        <v>176</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>536</v>
+      </c>
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40">
+        <v>186</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>546</v>
+      </c>
+      <c r="D40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" t="s">
+        <v>143</v>
+      </c>
+      <c r="G40" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41">
+        <v>196</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>556</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42">
+        <v>206</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>566</v>
+      </c>
+      <c r="D42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" t="s">
+        <v>148</v>
+      </c>
+      <c r="H42" t="s">
+        <v>100</v>
+      </c>
+      <c r="I42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43">
+        <v>216</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>576</v>
+      </c>
+      <c r="D43" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" t="s">
+        <v>151</v>
+      </c>
+      <c r="H43" t="s">
+        <v>152</v>
+      </c>
+      <c r="I43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44">
+        <v>226</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>586</v>
+      </c>
+      <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" t="s">
+        <v>154</v>
+      </c>
+      <c r="F44" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" t="s">
+        <v>155</v>
+      </c>
+      <c r="I44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45">
+        <v>236</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>596</v>
+      </c>
+      <c r="D45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" t="s">
+        <v>156</v>
+      </c>
+      <c r="F45" t="s">
+        <v>46</v>
+      </c>
+      <c r="G45" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45" t="s">
+        <v>99</v>
+      </c>
+      <c r="I45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Projet_2/Projet_2_31_mars.xlsx
+++ b/Projet_2/Projet_2_31_mars.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alext\OneDrive\Bureau\Génie physique\Calculs python\Labos-TPOP\Projet_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6902FBD3-E7FD-4700-AC5B-B0A09A2E494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50023B42-BE41-4CF0-ABDE-D4F215078555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{B802390F-8502-4048-A121-AD453CA8ECAD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{B802390F-8502-4048-A121-AD453CA8ECAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Valeurs de base" sheetId="2" r:id="rId1"/>
     <sheet name="Essai1" sheetId="1" r:id="rId2"/>
+    <sheet name="Essai2" sheetId="3" r:id="rId3"/>
+    <sheet name="Essai3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="182">
   <si>
     <t>Angle polariseur 1</t>
   </si>
@@ -514,6 +516,75 @@
   </si>
   <si>
     <t>angle</t>
+  </si>
+  <si>
+    <t>longueur</t>
+  </si>
+  <si>
+    <t>45.45g/100ml</t>
+  </si>
+  <si>
+    <t>42.8g/100ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 42.8 g / 100ml a 25 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 42.8 g / 100ml a 5 ml</t>
+  </si>
+  <si>
+    <t>(fructose)</t>
+  </si>
+  <si>
+    <t>(glucose)</t>
+  </si>
+  <si>
+    <t>Courant avec solution 42.8 g / 100ml a 10 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 42.8 g / 100ml a 15 ml</t>
+  </si>
+  <si>
+    <t>Courant avec solution 42.8 g / 100ml a 20 ml</t>
+  </si>
+  <si>
+    <t>À vide</t>
+  </si>
+  <si>
+    <t>15 ml de fructose + 20 ml de glucose</t>
+  </si>
+  <si>
+    <t>a vide</t>
+  </si>
+  <si>
+    <t>15 ml</t>
+  </si>
+  <si>
+    <t>25 ml</t>
+  </si>
+  <si>
+    <t>fuck python</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>vide</t>
+  </si>
+  <si>
+    <t>137.18 mm</t>
+  </si>
+  <si>
+    <t>106.65 mm</t>
+  </si>
+  <si>
+    <t>86.31 mm</t>
+  </si>
+  <si>
+    <t>65.96 mm</t>
+  </si>
+  <si>
+    <t>45.61 mm</t>
   </si>
 </sst>
 </file>
@@ -529,7 +600,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,6 +619,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -561,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -573,8 +650,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,1148 +1084,2445 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474AC0C1-7935-42B0-AFD9-FC74ED331F55}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.81640625" style="4" customWidth="1"/>
-    <col min="2" max="3" width="21.26953125" style="4" customWidth="1"/>
-    <col min="4" max="8" width="20.26953125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="22.1796875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="4"/>
+    <col min="2" max="2" width="21.26953125" style="4" customWidth="1"/>
+    <col min="3" max="7" width="20.26953125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="22.1796875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="11.453125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="3">
-        <v>25</v>
-      </c>
-      <c r="E2" s="3">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="C2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="4">
-        <v>246</v>
-      </c>
-      <c r="C3" s="5">
-        <f>B3</f>
-        <v>246</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="4">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="4">
+        <v>26</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="4">
+        <v>36</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="4">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="4">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="4">
+        <v>66</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="4">
+        <v>74</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="4">
+        <v>76</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="4">
+        <v>78</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="4">
+        <v>84</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <v>86</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="4">
+        <v>91</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="4">
+        <v>96</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="4">
+        <v>99</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="4">
+        <v>101</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="4">
+        <v>103</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="4">
+        <v>106</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="4">
+        <v>111</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="4">
+        <v>116</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="4">
+        <v>126</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="4">
+        <v>136</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="4">
+        <v>146</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="4">
+        <v>156</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <v>166</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
+        <v>176</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="4">
+        <v>186</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B30" s="4">
+        <v>196</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B31" s="4">
+        <v>206</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="4">
+        <v>216</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B33" s="4">
+        <v>226</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B34" s="4">
+        <v>236</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="4">
+        <v>246</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="4">
         <v>256</v>
       </c>
-      <c r="C4" s="5">
-        <f t="shared" ref="C4:C14" si="0">B4</f>
-        <v>256</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="F36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H36" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="4">
+    <row r="37" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="4">
         <v>266</v>
       </c>
-      <c r="C5" s="5">
-        <f t="shared" si="0"/>
-        <v>266</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H37" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="4">
+    <row r="38" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B38" s="4">
         <v>276</v>
       </c>
-      <c r="C6" s="5">
-        <f t="shared" si="0"/>
-        <v>276</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="F38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="H38" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="4">
+    <row r="39" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B39" s="4">
         <v>286</v>
       </c>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
-        <v>286</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="F39" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="H39" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="4">
+    <row r="40" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
         <v>296</v>
       </c>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
-        <v>296</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="F40" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="H40" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="4">
+    <row r="41" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B41" s="4">
         <v>306</v>
       </c>
-      <c r="C9" s="5">
-        <f t="shared" si="0"/>
-        <v>306</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="H41" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="4">
+    <row r="42" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B42" s="4">
         <v>316</v>
       </c>
-      <c r="C10" s="5">
-        <f t="shared" si="0"/>
-        <v>316</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="H42" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="4">
+    <row r="43" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B43" s="4">
         <v>326</v>
       </c>
-      <c r="C11" s="4">
-        <f t="shared" si="0"/>
-        <v>326</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
+    <row r="44" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B44" s="4">
         <v>336</v>
       </c>
-      <c r="C12" s="4">
-        <f t="shared" si="0"/>
-        <v>336</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="4">
+    <row r="45" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B45" s="4">
         <v>346</v>
       </c>
-      <c r="C13" s="4">
-        <f t="shared" si="0"/>
-        <v>346</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C45" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="4">
+    <row r="46" spans="2:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B46" s="4">
         <v>356</v>
       </c>
-      <c r="C14" s="4">
-        <f t="shared" si="0"/>
-        <v>356</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="4">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4">
-        <f>B15+360</f>
-        <v>366</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="4">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4">
-        <f t="shared" ref="C16:C46" si="1">B16+360</f>
-        <v>376</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B17" s="4">
-        <v>26</v>
-      </c>
-      <c r="C17" s="4">
-        <f t="shared" si="1"/>
-        <v>386</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="4">
-        <v>36</v>
-      </c>
-      <c r="C18" s="4">
-        <f t="shared" si="1"/>
-        <v>396</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="4">
-        <v>46</v>
-      </c>
-      <c r="C19" s="4">
-        <f t="shared" si="1"/>
-        <v>406</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="4">
-        <v>56</v>
-      </c>
-      <c r="C20" s="4">
-        <f t="shared" si="1"/>
-        <v>416</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="4">
-        <v>66</v>
-      </c>
-      <c r="C21" s="4">
-        <f t="shared" si="1"/>
-        <v>426</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B22" s="4">
-        <v>74</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="4">
-        <v>76</v>
-      </c>
-      <c r="C23" s="4">
-        <f t="shared" si="1"/>
-        <v>436</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="4">
-        <v>78</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B25" s="4">
-        <v>84</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="4">
-        <v>86</v>
-      </c>
-      <c r="C26" s="4">
-        <f t="shared" si="1"/>
-        <v>446</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B27" s="4">
-        <v>91</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B28" s="4">
-        <v>96</v>
-      </c>
-      <c r="C28" s="4">
-        <f t="shared" si="1"/>
-        <v>456</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B29" s="4">
-        <v>99</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B30" s="4">
-        <v>101</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="4">
-        <v>103</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="4">
-        <v>106</v>
-      </c>
-      <c r="C32" s="4">
-        <f t="shared" si="1"/>
-        <v>466</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B33" s="4">
-        <v>111</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B34" s="4">
-        <v>116</v>
-      </c>
-      <c r="C34" s="4">
-        <f t="shared" si="1"/>
-        <v>476</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B35" s="4">
-        <v>126</v>
-      </c>
-      <c r="C35" s="4">
-        <f t="shared" si="1"/>
-        <v>486</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B36" s="4">
-        <v>136</v>
-      </c>
-      <c r="C36" s="4">
-        <f t="shared" si="1"/>
-        <v>496</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B37" s="4">
-        <v>146</v>
-      </c>
-      <c r="C37" s="4">
-        <f t="shared" si="1"/>
-        <v>506</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B38" s="4">
-        <v>156</v>
-      </c>
-      <c r="C38" s="4">
-        <f t="shared" si="1"/>
-        <v>516</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B39" s="4">
-        <v>166</v>
-      </c>
-      <c r="C39" s="4">
-        <f t="shared" si="1"/>
-        <v>526</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B40" s="4">
-        <v>176</v>
-      </c>
-      <c r="C40" s="4">
-        <f t="shared" si="1"/>
-        <v>536</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B41" s="4">
-        <v>186</v>
-      </c>
-      <c r="C41" s="4">
-        <f t="shared" si="1"/>
-        <v>546</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B42" s="4">
-        <v>196</v>
-      </c>
-      <c r="C42" s="4">
-        <f t="shared" si="1"/>
-        <v>556</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B43" s="4">
-        <v>206</v>
-      </c>
-      <c r="C43" s="4">
-        <f t="shared" si="1"/>
-        <v>566</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B44" s="4">
-        <v>216</v>
-      </c>
-      <c r="C44" s="4">
-        <f t="shared" si="1"/>
-        <v>576</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B45" s="4">
-        <v>226</v>
-      </c>
-      <c r="C45" s="4">
-        <f t="shared" si="1"/>
-        <v>586</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B46" s="4">
-        <v>236</v>
-      </c>
-      <c r="C46" s="4">
-        <f t="shared" si="1"/>
-        <v>596</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="2:10" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BAAEE1-B9F4-434B-97D4-F2D018AE8BBB}">
+  <dimension ref="A1:H85"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+    <col min="3" max="12" width="22.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="5">
+        <v>35.43</v>
+      </c>
+      <c r="D2" s="5">
+        <v>60.87</v>
+      </c>
+      <c r="E2" s="5">
+        <v>86.31</v>
+      </c>
+      <c r="F2" s="5">
+        <v>111.74</v>
+      </c>
+      <c r="G2" s="5">
+        <v>137.18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>8.4</v>
+      </c>
+      <c r="D3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E3">
+        <v>2.7</v>
+      </c>
+      <c r="F3">
+        <v>3.4</v>
+      </c>
+      <c r="G3">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3.3</v>
+      </c>
+      <c r="F4">
+        <v>6.2</v>
+      </c>
+      <c r="G4">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>2.7</v>
+      </c>
+      <c r="D5">
+        <v>3.6</v>
+      </c>
+      <c r="E5">
+        <v>5.9</v>
+      </c>
+      <c r="F5">
+        <v>10.5</v>
+      </c>
+      <c r="G5">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="4">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>3.4</v>
+      </c>
+      <c r="D6">
+        <v>6.5</v>
+      </c>
+      <c r="E6">
+        <v>10.7</v>
+      </c>
+      <c r="F6">
+        <v>16.3</v>
+      </c>
+      <c r="G6">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="4">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>6.2</v>
+      </c>
+      <c r="D7">
+        <v>11.4</v>
+      </c>
+      <c r="E7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F7">
+        <v>22.6</v>
+      </c>
+      <c r="G7">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>17.2</v>
+      </c>
+      <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>28.4</v>
+      </c>
+      <c r="G8">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>17.5</v>
+      </c>
+      <c r="D9">
+        <v>23.6</v>
+      </c>
+      <c r="E9">
+        <v>29.1</v>
+      </c>
+      <c r="F9">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="G9">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>24.9</v>
+      </c>
+      <c r="D10">
+        <v>30.1</v>
+      </c>
+      <c r="E10">
+        <v>34.5</v>
+      </c>
+      <c r="F10">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="G10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>30.8</v>
+      </c>
+      <c r="D11">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E11">
+        <v>38.1</v>
+      </c>
+      <c r="F11">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="G11">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+      <c r="B12" s="7">
+        <v>85</v>
+      </c>
+      <c r="E12">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="F12">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="G12">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="D13">
+        <v>40</v>
+      </c>
+      <c r="E13" s="6">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="F13">
+        <v>37.4</v>
+      </c>
+      <c r="G13">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+      <c r="B14" s="7">
+        <v>95</v>
+      </c>
+      <c r="D14">
+        <v>41.1</v>
+      </c>
+      <c r="E14">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="D15" s="6">
+        <v>41.9</v>
+      </c>
+      <c r="E15">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>35.1</v>
+      </c>
+      <c r="G15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+      <c r="B16" s="7">
+        <v>105</v>
+      </c>
+      <c r="D16">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4">
+        <v>110</v>
+      </c>
+      <c r="C17" s="6">
+        <v>41.8</v>
+      </c>
+      <c r="D17">
+        <v>40.5</v>
+      </c>
+      <c r="E17">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F17">
+        <v>30.5</v>
+      </c>
+      <c r="G17">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="4"/>
+      <c r="B18" s="7">
+        <v>115</v>
+      </c>
+      <c r="C18">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4">
+        <v>120</v>
+      </c>
+      <c r="C19">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D19">
+        <v>37.9</v>
+      </c>
+      <c r="E19">
+        <v>31.1</v>
+      </c>
+      <c r="F19">
+        <v>24.3</v>
+      </c>
+      <c r="G19">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4">
+        <v>130</v>
+      </c>
+      <c r="C20">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="D20">
+        <v>33.4</v>
+      </c>
+      <c r="E20">
+        <v>25.4</v>
+      </c>
+      <c r="F20">
+        <v>18.2</v>
+      </c>
+      <c r="G20">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4">
+        <v>140</v>
+      </c>
+      <c r="C21">
+        <v>33.1</v>
+      </c>
+      <c r="D21">
+        <v>27.2</v>
+      </c>
+      <c r="E21">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="F21">
+        <v>11.6</v>
+      </c>
+      <c r="G21">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4">
+        <v>150</v>
+      </c>
+      <c r="C22">
+        <v>27.5</v>
+      </c>
+      <c r="D22">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E22">
+        <v>13.1</v>
+      </c>
+      <c r="F22">
+        <v>6.8</v>
+      </c>
+      <c r="G22">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4">
+        <v>160</v>
+      </c>
+      <c r="C23">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D23">
+        <v>13.9</v>
+      </c>
+      <c r="E23">
+        <v>7.8</v>
+      </c>
+      <c r="F23">
+        <v>3.8</v>
+      </c>
+      <c r="G23">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4">
+        <v>170</v>
+      </c>
+      <c r="C24">
+        <v>13.8</v>
+      </c>
+      <c r="D24">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E24">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F24">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G24">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4">
+        <v>180</v>
+      </c>
+      <c r="C25">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D25">
+        <v>4.3</v>
+      </c>
+      <c r="E25">
+        <v>2.5</v>
+      </c>
+      <c r="F25">
+        <v>2.9</v>
+      </c>
+      <c r="G25">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4">
+        <v>190</v>
+      </c>
+      <c r="C26">
+        <v>4.3</v>
+      </c>
+      <c r="D26">
+        <v>2.6</v>
+      </c>
+      <c r="E26">
+        <v>3.1</v>
+      </c>
+      <c r="F26">
+        <v>5.8</v>
+      </c>
+      <c r="G26">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <v>200</v>
+      </c>
+      <c r="C27">
+        <v>2.6</v>
+      </c>
+      <c r="D27">
+        <v>3.3</v>
+      </c>
+      <c r="E27">
+        <v>6.2</v>
+      </c>
+      <c r="F27">
+        <v>10.5</v>
+      </c>
+      <c r="G27">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="4">
+        <v>210</v>
+      </c>
+      <c r="C28">
+        <v>3.5</v>
+      </c>
+      <c r="D28">
+        <v>6.3</v>
+      </c>
+      <c r="E28">
+        <v>11.1</v>
+      </c>
+      <c r="F28">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G28">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="4">
+        <v>220</v>
+      </c>
+      <c r="C29">
+        <v>6.6</v>
+      </c>
+      <c r="D29">
+        <v>11.2</v>
+      </c>
+      <c r="E29">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F29">
+        <v>23.2</v>
+      </c>
+      <c r="G29">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="4">
+        <v>230</v>
+      </c>
+      <c r="C30">
+        <v>11.2</v>
+      </c>
+      <c r="D30">
+        <v>17.7</v>
+      </c>
+      <c r="E30">
+        <v>23.4</v>
+      </c>
+      <c r="F30">
+        <v>28.5</v>
+      </c>
+      <c r="G30">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="4">
+        <v>240</v>
+      </c>
+      <c r="C31">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D31">
+        <v>24.6</v>
+      </c>
+      <c r="E31">
+        <v>29.5</v>
+      </c>
+      <c r="F31">
+        <v>34</v>
+      </c>
+      <c r="G31">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="4">
+        <v>250</v>
+      </c>
+      <c r="C32">
+        <v>24.6</v>
+      </c>
+      <c r="D32">
+        <v>31.2</v>
+      </c>
+      <c r="E32">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="F32">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="G32">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="7">
+        <v>255</v>
+      </c>
+      <c r="F33">
+        <v>38.200000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="4">
+        <v>260</v>
+      </c>
+      <c r="C34">
+        <v>31.2</v>
+      </c>
+      <c r="D34">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="E34">
+        <v>38.1</v>
+      </c>
+      <c r="F34">
+        <v>39.4</v>
+      </c>
+      <c r="G34">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="7">
+        <v>265</v>
+      </c>
+      <c r="F35">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="4">
+        <v>270</v>
+      </c>
+      <c r="C36">
+        <v>36.6</v>
+      </c>
+      <c r="D36">
+        <v>40.5</v>
+      </c>
+      <c r="E36">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F36">
+        <v>38.4</v>
+      </c>
+      <c r="G36">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="7">
+        <v>275</v>
+      </c>
+      <c r="D37">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="4">
+        <v>280</v>
+      </c>
+      <c r="C38">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D38">
+        <v>42.3</v>
+      </c>
+      <c r="E38">
+        <v>39</v>
+      </c>
+      <c r="F38">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G38">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="7">
+        <v>285</v>
+      </c>
+      <c r="D39">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
+        <v>290</v>
+      </c>
+      <c r="C40">
+        <v>42.6</v>
+      </c>
+      <c r="D40">
+        <v>41.5</v>
+      </c>
+      <c r="E40">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="F40">
+        <v>30.7</v>
+      </c>
+      <c r="G40">
+        <v>22.2</v>
+      </c>
+      <c r="H40">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="7">
+        <v>295</v>
+      </c>
+      <c r="C41">
+        <v>42.8</v>
+      </c>
+      <c r="H41">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="4">
+        <v>300</v>
+      </c>
+      <c r="C42">
+        <v>42.3</v>
+      </c>
+      <c r="D42">
+        <v>38.5</v>
+      </c>
+      <c r="E42">
+        <v>31.8</v>
+      </c>
+      <c r="F42">
+        <v>25.1</v>
+      </c>
+      <c r="G42">
+        <v>16.3</v>
+      </c>
+      <c r="H42">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="4">
+        <v>305</v>
+      </c>
+      <c r="H43">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="4">
+        <v>310</v>
+      </c>
+      <c r="C44">
+        <v>39.6</v>
+      </c>
+      <c r="D44">
+        <v>33.6</v>
+      </c>
+      <c r="E44">
+        <v>25.9</v>
+      </c>
+      <c r="F44">
+        <v>18.7</v>
+      </c>
+      <c r="G44">
+        <v>10.8</v>
+      </c>
+      <c r="H44">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="4">
+        <v>320</v>
+      </c>
+      <c r="C45">
+        <v>34.5</v>
+      </c>
+      <c r="D45">
+        <v>27.3</v>
+      </c>
+      <c r="E45">
+        <v>19.8</v>
+      </c>
+      <c r="F45">
+        <v>12.6</v>
+      </c>
+      <c r="G45">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="4">
+        <v>330</v>
+      </c>
+      <c r="C46">
+        <v>28.3</v>
+      </c>
+      <c r="D46">
+        <v>20.6</v>
+      </c>
+      <c r="E46">
+        <v>13.4</v>
+      </c>
+      <c r="F46">
+        <v>7.6</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="4">
+        <v>340</v>
+      </c>
+      <c r="C47">
+        <v>21.3</v>
+      </c>
+      <c r="D47">
+        <v>14.1</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G47">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="4">
+        <v>350</v>
+      </c>
+      <c r="C48">
+        <v>14.1</v>
+      </c>
+      <c r="D48">
+        <v>8.4</v>
+      </c>
+      <c r="E48">
+        <v>4.2</v>
+      </c>
+      <c r="F48">
+        <v>2.6</v>
+      </c>
+      <c r="G48">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4">
+        <v>360</v>
+      </c>
+      <c r="C49">
+        <v>8.4</v>
+      </c>
+      <c r="D49">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E49">
+        <v>2.7</v>
+      </c>
+      <c r="F49">
+        <v>3.4</v>
+      </c>
+      <c r="G49">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="4"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="4"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B60" s="4"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B61" s="4"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" s="4"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" s="4"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" s="4"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" s="4"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="4"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045AE05D-0D5D-4166-98CA-C97F8AF27DBA}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="8" width="23.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>14.5</v>
+      </c>
+      <c r="D3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E3">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>8.5</v>
+      </c>
+      <c r="D4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E4">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="4">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="4">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>7.3</v>
+      </c>
+      <c r="D8">
+        <v>9.1</v>
+      </c>
+      <c r="E8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>12.8</v>
+      </c>
+      <c r="D9">
+        <v>14.8</v>
+      </c>
+      <c r="E9">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>19.3</v>
+      </c>
+      <c r="D10">
+        <v>20.8</v>
+      </c>
+      <c r="E10">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>26.6</v>
+      </c>
+      <c r="D11">
+        <v>27.2</v>
+      </c>
+      <c r="E11">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>33.5</v>
+      </c>
+      <c r="D12">
+        <v>33.1</v>
+      </c>
+      <c r="E12">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+      <c r="B14" s="7">
+        <v>105</v>
+      </c>
+      <c r="D14">
+        <v>38.9</v>
+      </c>
+      <c r="E14">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+      <c r="B15" s="7">
+        <v>107</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4">
+        <v>110</v>
+      </c>
+      <c r="C16">
+        <v>43.1</v>
+      </c>
+      <c r="D16">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+      <c r="B17" s="7">
+        <v>112</v>
+      </c>
+      <c r="E17" s="6">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4"/>
+      <c r="B18" s="7">
+        <v>115</v>
+      </c>
+      <c r="C18">
+        <v>43.6</v>
+      </c>
+      <c r="D18" s="6">
+        <v>40</v>
+      </c>
+      <c r="E18">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+      <c r="B19" s="7">
+        <v>117</v>
+      </c>
+      <c r="D19">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="E19">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4">
+        <v>120</v>
+      </c>
+      <c r="C20" s="6">
+        <v>44.7</v>
+      </c>
+      <c r="D20">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E20">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4"/>
+      <c r="B21" s="7">
+        <v>125</v>
+      </c>
+      <c r="C21">
+        <v>43.8</v>
+      </c>
+      <c r="D21">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4">
+        <v>130</v>
+      </c>
+      <c r="C22">
+        <v>43.9</v>
+      </c>
+      <c r="D22">
+        <v>37.6</v>
+      </c>
+      <c r="E22">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4">
+        <v>140</v>
+      </c>
+      <c r="C23">
+        <v>40.6</v>
+      </c>
+      <c r="D23">
+        <v>33.1</v>
+      </c>
+      <c r="E23">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4">
+        <v>150</v>
+      </c>
+      <c r="C24">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>27.5</v>
+      </c>
+      <c r="E24">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4">
+        <v>160</v>
+      </c>
+      <c r="C25">
+        <v>28.3</v>
+      </c>
+      <c r="D25">
+        <v>21.6</v>
+      </c>
+      <c r="E25">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4">
+        <v>170</v>
+      </c>
+      <c r="C26">
+        <v>21</v>
+      </c>
+      <c r="D26">
+        <v>14.9</v>
+      </c>
+      <c r="E26">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4">
+        <v>180</v>
+      </c>
+      <c r="C27">
+        <v>13.9</v>
+      </c>
+      <c r="D27">
+        <v>9.1</v>
+      </c>
+      <c r="E27">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Projet_2/Projet_2_31_mars.xlsx
+++ b/Projet_2/Projet_2_31_mars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alext\OneDrive\Bureau\Génie physique\Calculs python\Labos-TPOP\Projet_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50023B42-BE41-4CF0-ABDE-D4F215078555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5A81AD-F582-4146-AB9D-385D50F7A729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{B802390F-8502-4048-A121-AD453CA8ECAD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
   <si>
     <t>Angle polariseur 1</t>
   </si>
@@ -572,19 +572,31 @@
     <t>vide</t>
   </si>
   <si>
-    <t>137.18 mm</t>
-  </si>
-  <si>
-    <t>106.65 mm</t>
-  </si>
-  <si>
-    <t>86.31 mm</t>
-  </si>
-  <si>
-    <t>65.96 mm</t>
-  </si>
-  <si>
-    <t>45.61 mm</t>
+    <t>[ 35.435  55.783  76.131  96.479 127.001]</t>
+  </si>
+  <si>
+    <t>35.435 mm</t>
+  </si>
+  <si>
+    <t>55.783 mm</t>
+  </si>
+  <si>
+    <t>76.131 mm</t>
+  </si>
+  <si>
+    <t>96.479 mm</t>
+  </si>
+  <si>
+    <t>127.001 mm</t>
+  </si>
+  <si>
+    <t>25.261 mm</t>
+  </si>
+  <si>
+    <t>50.696 mm</t>
+  </si>
+  <si>
+    <t>101.566 mm</t>
   </si>
 </sst>
 </file>
@@ -1103,19 +1115,19 @@
         <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>14</v>
@@ -1129,19 +1141,19 @@
         <v>158</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>176</v>
@@ -1152,19 +1164,19 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>82</v>
@@ -1178,19 +1190,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>85</v>
@@ -1204,19 +1216,19 @@
         <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>84</v>
@@ -1230,19 +1242,19 @@
         <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>89</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>38</v>
@@ -1253,19 +1265,19 @@
         <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>93</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>33</v>
@@ -1276,42 +1288,45 @@
         <v>56</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="B9" s="4">
         <v>66</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>101</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>102</v>
@@ -1321,7 +1336,7 @@
       <c r="B10" s="4">
         <v>74</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1330,19 +1345,19 @@
         <v>76</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>107</v>
@@ -1352,22 +1367,22 @@
       <c r="B12" s="4">
         <v>78</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B13" s="4">
         <v>84</v>
       </c>
+      <c r="D13" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E13" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
@@ -1375,19 +1390,19 @@
         <v>86</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>60</v>
@@ -1397,11 +1412,11 @@
       <c r="B15" s="4">
         <v>91</v>
       </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="E15" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
@@ -1409,19 +1424,19 @@
         <v>96</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>87</v>
@@ -1431,7 +1446,7 @@
       <c r="B17" s="4">
         <v>99</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1439,7 +1454,7 @@
       <c r="B18" s="4">
         <v>101</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1447,7 +1462,7 @@
       <c r="B19" s="4">
         <v>103</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1456,19 +1471,19 @@
         <v>106</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>116</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>119</v>
@@ -1478,7 +1493,7 @@
       <c r="B21" s="4">
         <v>111</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1487,19 +1502,19 @@
         <v>116</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>123</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>125</v>
@@ -1510,19 +1525,19 @@
         <v>126</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>127</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>68</v>
@@ -1533,19 +1548,19 @@
         <v>136</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>130</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>76</v>
@@ -1556,19 +1571,19 @@
         <v>146</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>79</v>
@@ -1579,19 +1594,19 @@
         <v>156</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>71</v>
@@ -1602,19 +1617,19 @@
         <v>166</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>141</v>
@@ -1625,19 +1640,19 @@
         <v>176</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>62</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>70</v>
@@ -1648,19 +1663,19 @@
         <v>186</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>143</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>145</v>
@@ -1671,19 +1686,19 @@
         <v>196</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>145</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>83</v>
@@ -1694,19 +1709,19 @@
         <v>206</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>147</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>149</v>
@@ -1717,19 +1732,19 @@
         <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>150</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>153</v>
@@ -1740,19 +1755,19 @@
         <v>226</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>61</v>
+        <v>155</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>128</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>56</v>
@@ -1763,19 +1778,19 @@
         <v>236</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>157</v>
@@ -1786,19 +1801,19 @@
         <v>246</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>20</v>
@@ -1815,19 +1830,19 @@
         <v>256</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>27</v>
@@ -1838,19 +1853,19 @@
         <v>266</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>33</v>
@@ -1861,19 +1876,19 @@
         <v>276</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>38</v>
@@ -1884,19 +1899,19 @@
         <v>286</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>43</v>
@@ -1907,19 +1922,19 @@
         <v>296</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>48</v>
@@ -1930,19 +1945,19 @@
         <v>306</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>51</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>54</v>
@@ -1953,19 +1968,19 @@
         <v>316</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>56</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>59</v>
@@ -1976,19 +1991,19 @@
         <v>326</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>62</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>65</v>
@@ -1999,19 +2014,19 @@
         <v>336</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>71</v>
@@ -2022,19 +2037,19 @@
         <v>346</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>70</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>75</v>
@@ -2045,7 +2060,7 @@
         <v>356</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>77</v>
@@ -2057,7 +2072,7 @@
         <v>77</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>78</v>
@@ -2075,7 +2090,7 @@
   <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.1796875" customWidth="1"/>
+    <col min="1" max="1" width="31.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.7265625" customWidth="1"/>
     <col min="3" max="12" width="22.453125" customWidth="1"/>
   </cols>
@@ -2113,20 +2128,20 @@
       <c r="B2" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="5">
-        <v>35.43</v>
-      </c>
-      <c r="D2" s="5">
-        <v>60.87</v>
-      </c>
-      <c r="E2" s="5">
-        <v>86.31</v>
-      </c>
-      <c r="F2" s="5">
-        <v>111.74</v>
-      </c>
-      <c r="G2" s="5">
-        <v>137.18</v>
+      <c r="C2" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="H2" t="s">
         <v>176</v>
@@ -3152,10 +3167,10 @@
         <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
